--- a/AAII_Financials/Quarterly/VTRS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VTRS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>VTRS</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3756800</v>
+      </c>
+      <c r="E8" s="3">
         <v>3517000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3703600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3759900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3582100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3254300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3528100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3751200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3796600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3663400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3837300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3941900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3918600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3729100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3876000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4078200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4116800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4191700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4341600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4536600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4577800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4430300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3623500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2972100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2731200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2619200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3191800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2961700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2851500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2495500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3078700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2185100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2139200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2210800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2262000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2152400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2019500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2038700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2145300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2303500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2120900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2154600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2210700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2197100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2132200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2285900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2236000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2350500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2357400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2558800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2734000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3071000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2962600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2500400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1711900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1600600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1591300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1865100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1804300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1718500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1560700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1819200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1571700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1377800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1492800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1497900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1429700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1234800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1489400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1605900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1493100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1542500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1682700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1731200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1721500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1596900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1590100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1842200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1766300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1834300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1782800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1802600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1506800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1467700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1123100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1260200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1130600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1027900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1326700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1157400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1133000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>934800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1259500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,103 +1125,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>245200</v>
+      </c>
+      <c r="E12" s="3">
         <v>245800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>271200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>244800</v>
       </c>
-      <c r="G12" s="3">
-        <v>216000</v>
-      </c>
       <c r="H12" s="3">
+        <v>217400</v>
+      </c>
+      <c r="I12" s="3">
         <v>221300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>206500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>198400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>203700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>197300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>202700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>210900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>207900</v>
-      </c>
-      <c r="P12" s="3">
-        <v>180900</v>
       </c>
       <c r="Q12" s="3">
         <v>180900</v>
       </c>
       <c r="R12" s="3">
+        <v>180900</v>
+      </c>
+      <c r="S12" s="3">
         <v>174900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>162000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>142000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>194700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>153100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>143800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>163000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>153300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>126000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>115700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>112300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>131200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>127600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>120500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>139400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>130300</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,148 +1319,154 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>429400</v>
+      </c>
+      <c r="E14" s="3">
         <v>393500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>531000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>326600</v>
       </c>
-      <c r="G14" s="3">
-        <v>471800</v>
-      </c>
       <c r="H14" s="3">
+        <v>456400</v>
+      </c>
+      <c r="I14" s="3">
         <v>3103500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>769700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>336600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>617000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>59300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1345900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>28300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>37300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>103500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>549700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>221700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>217800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>166900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>704900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>313700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>420200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>604700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1003000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>209900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>328500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>145700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>333300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>113500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>274400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>190300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>664900</v>
+      </c>
+      <c r="E15" s="3">
         <v>676100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>692900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>688500</v>
       </c>
-      <c r="G15" s="3">
-        <v>678300</v>
-      </c>
       <c r="H15" s="3">
+        <v>676100</v>
+      </c>
+      <c r="I15" s="3">
         <v>664700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>561600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>669700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>786300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>691000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>583100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>679400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>686700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>730000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>3285300</v>
+      </c>
+      <c r="E17" s="3">
         <v>3278400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3415400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3355300</v>
       </c>
-      <c r="G17" s="3">
-        <v>3225700</v>
-      </c>
       <c r="H17" s="3">
+        <v>3241100</v>
+      </c>
+      <c r="I17" s="3">
         <v>3171300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3203700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3252200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3444600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3238400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3326000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3370800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3371800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3204000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4072900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3524400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3568500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3485800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4424900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4181300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4625600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4696500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4505000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2620700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2613100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2434900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2930200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2638000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2756000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2471500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2845800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>471500</v>
+      </c>
+      <c r="E18" s="3">
         <v>238600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>288200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>404600</v>
       </c>
-      <c r="G18" s="3">
-        <v>356400</v>
-      </c>
       <c r="H18" s="3">
+        <v>341000</v>
+      </c>
+      <c r="I18" s="3">
         <v>83000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>324400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>499000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>352000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>425000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>511300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>571100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>546800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>525100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-196900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>553800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>548300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>705900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-83300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>355300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-47800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-266200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-881500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>351400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>118100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>184300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>261600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>323700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>95500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>24000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>232900</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1749,483 +1782,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-27700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-19400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-33700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-14900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-39000</v>
       </c>
       <c r="I20" s="3">
         <v>-39000</v>
       </c>
       <c r="J20" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-77100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-19000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>22700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-120500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>32800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-48100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1812900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>26900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-32200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>27600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>12400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>18100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-33700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-16400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1151000</v>
+      </c>
+      <c r="E21" s="3">
         <v>942400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1000500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1126800</v>
       </c>
-      <c r="G21" s="3">
-        <v>1049600</v>
-      </c>
       <c r="H21" s="3">
+        <v>1032000</v>
+      </c>
+      <c r="I21" s="3">
         <v>786700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>925000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1245800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1157300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1093300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1214900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1251400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1200700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1303200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2485800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1280200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1257500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1409700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>694100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1368900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1265100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1150200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>84000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>791200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>551900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>565600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>808900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>784400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>580500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>517200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>821100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E22" s="3">
         <v>120100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>119600</v>
       </c>
       <c r="F22" s="3">
         <v>119600</v>
       </c>
       <c r="G22" s="3">
+        <v>119600</v>
+      </c>
+      <c r="H22" s="3">
         <v>116600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>115500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>120200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>149000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>145800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>138400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>140900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>141500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>143700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>147000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>147100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>153200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>145900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>146200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>148200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>151900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>167100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>169000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>144400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>117300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>116200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>119900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>126000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>128900</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>131200</v>
       </c>
       <c r="AF22" s="3">
         <v>131200</v>
       </c>
       <c r="AG22" s="3">
+        <v>131200</v>
+      </c>
+      <c r="AH22" s="3">
         <v>135200</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-247300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-343000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-217100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3097000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-526500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>90500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-391800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>204600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-855000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>402200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>333000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>322700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1468900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>427500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>389300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>527500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-203900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>199900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-219100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-441300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1013500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>241600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>30700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>135200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>185800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-52100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-114500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-423700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>120300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-212500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-55000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-65400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>90700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-89400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>70600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>69000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>98000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>457700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>73200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>75400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>128300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>59900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-111600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>60100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>596300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-97700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>55900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>114700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>116400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-89500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E26" s="3">
         <v>176400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-340100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-128200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3042000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-516500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>94800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-326400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>113900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-765600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>331600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>264000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>224700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1011200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>354300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>313900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>399200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-263800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>311500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-279200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1037600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-915800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>185700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>39400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>20800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>20500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>189800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-168500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>58000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E27" s="3">
         <v>176400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-340100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-128200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3042000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-516500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>94800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-326400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>113900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-765600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>331600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>264000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>224700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1011200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>354300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>313900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>399200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-263800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>311500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-279200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1037600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-915800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>185700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>39400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>20800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>20500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>189800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-168500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>58000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2678,8 +2739,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -2696,11 +2757,14 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E32" s="3">
         <v>27700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>19400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>33700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>14900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>39000</v>
       </c>
       <c r="I32" s="3">
         <v>39000</v>
       </c>
       <c r="J32" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K32" s="3">
         <v>77100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>19000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-22700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>120500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-32800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>48100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1812900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-26900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>32200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-27600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>33700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>9000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>16400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E33" s="3">
         <v>176400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-340100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-128200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3042000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-516500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>94800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-326400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>113900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-765600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>331600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>264000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>224700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1011200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>354300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>313900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>399200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-263800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>311500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-279200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1037600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-915800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>185700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>39400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>20800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>20500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>189800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-168500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>51200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E35" s="3">
         <v>176400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-340100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-128200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3042000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-516500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>94800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-326400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>113900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-765600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>331600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>264000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>224700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1011200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>354300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>313900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>399200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-263800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>311500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-279200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1037600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-915800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>185700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>39400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>20800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>20500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>189800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-168500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>51200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,607 +3525,626 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>886500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1804200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1322400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>975300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>566400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>755000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>734800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1878700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>917200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1014600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>991900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1309600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>629200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>506600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1259900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>646700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>664700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>752400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>701200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>756600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>673900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>806900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>844400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>664500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>323600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>572400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>475600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>358900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>211500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>229800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>388100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>624000</v>
+      </c>
+      <c r="E42" s="3">
         <v>596000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>190600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>181800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>242200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>247200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>355100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>169000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>102000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>90800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>192500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>80200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>82200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>81000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>77900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>74300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>77200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>84600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>89200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>87700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>88100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>85400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>84900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>80000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>77600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>69500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>65800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>63500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>63100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>61700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3669500</v>
+      </c>
+      <c r="E43" s="3">
         <v>3742000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3347100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3587200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3597300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3388500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3522000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4103200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4018300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4271000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4361800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3906000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3772100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3497500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3814500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3333900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3736200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4093900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4266400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4345500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4478700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4529000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4843800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2964100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2753200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2774600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3058800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2948000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2703800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2778500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2881000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3933200</v>
+      </c>
+      <c r="E44" s="3">
         <v>3927000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3999200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4111400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4264300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4096400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3854100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4084600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3942100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3823200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3469700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3671900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3641500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3664300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3519500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3380400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3612500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3797300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3977700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4081900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4487600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4942200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5471900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3022000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2785700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2639600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2670900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2763500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2776200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2708800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2580200</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>750400</v>
+      </c>
+      <c r="E45" s="3">
         <v>662100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>704500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>909600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>924500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>964800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>913800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>937700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2650700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3545000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3804300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1797400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1447200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1641200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1963600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3052500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3085900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3016100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1868400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2036700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2021500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1955000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1622500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>604100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>524500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>544400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>486200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>511200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>510800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>483500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>460900</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10055700</v>
+      </c>
+      <c r="E46" s="3">
         <v>10916800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9789200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9951400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9774600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9622400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9520700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11307700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11792100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12923500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12976100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10932000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9778000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9630300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10635400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10487800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11176500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11744300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10902900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11308400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11749800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12318500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12867500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7334700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6464600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6600500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6757300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6645100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6265400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6262300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6367700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="3">
         <v>815000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>850000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>950000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1234000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1349800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1477100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1437700</v>
-      </c>
-      <c r="L47" s="3">
-        <v>165700</v>
       </c>
       <c r="M47" s="3">
         <v>165700</v>
@@ -4048,16 +4153,16 @@
         <v>165700</v>
       </c>
       <c r="O47" s="3">
+        <v>165700</v>
+      </c>
+      <c r="P47" s="3">
         <v>154200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>78600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>94000</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>24</v>
@@ -4065,237 +4170,246 @@
       <c r="T47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
         <v>11600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>24200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>33600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>47900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>57600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>71400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>81100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>92200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>106600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>118400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>127400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>138700</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2698800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2780900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2885300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2892100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2918900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2901500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2919200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2944500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2936000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2950300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3005200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3174300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3233600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3261600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3283800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3303200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3359000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3431900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3479400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3419900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3472000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3558300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3783500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2286200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2267700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2303400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2404200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2382800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2396800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2387600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2170200</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20331300</v>
+      </c>
+      <c r="E49" s="3">
         <v>21174700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21856800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22453700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23072100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23124400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>26204200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>27540600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>27744900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28827200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29048200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>31558600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>32616900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>33274800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>33032900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>33067900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>34624100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>36230600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>38247900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>39156500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>39854100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>40396900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>42030200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>20783100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>20479200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>20373600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>21240500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21211400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>22423600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>22563400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>23412400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4601,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>801100</v>
+      </c>
+      <c r="E52" s="3">
         <v>853000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>785600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>774200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>771600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>775000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>754000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>721100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>734000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1823800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1797400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1981600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1946500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2085800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2976100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1803700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1965500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2060100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2212600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2174000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2884000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2671900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2823900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>781500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>872500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>787300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>761300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>707600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>612700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>565900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>645900</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>35044600</v>
+      </c>
+      <c r="E54" s="3">
         <v>36834600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37193100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37920400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38411500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38474900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>41500900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44754100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45330000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47343700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>47685500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>48742600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>48695200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49290200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>50022200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>48662600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>51125100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>53466900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>54842800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>56070400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>57984100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58979200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>61553000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>31243100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30155400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30145900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>31255500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>31053500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>31816900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>31906600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>32734900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +4969,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1726500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1749400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1754100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1793400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1782600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1988400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1853700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1925900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1957500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2196900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1938200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1989100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1962000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1957500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1158000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>791200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1050700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>928400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1056100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1139000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1319500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1549700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1345700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>900800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1256700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1273500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1528100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1511300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1538200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1316500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1617000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1851500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2029300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2039300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2106600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1837400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>109300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>87700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1540600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2448500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1981500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2017700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1387200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1434100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>788200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1250500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1255400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1778300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3250800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3353300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3587900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3448900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2292200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3357200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3182900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3144400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1433900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1457600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>554500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>700200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>655300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>657100</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>920600</v>
+      </c>
+      <c r="E59" s="3">
         <v>997000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1154100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1006500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1312500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1391500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1596600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1711400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1198200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1448200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1669900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1352900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1259200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1390400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4337700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4474800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4852200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5463700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5475000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5377000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5364200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6136200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5860000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3191700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2570200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2520800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2583400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2579200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2321900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2185800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2313700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6345800</v>
+      </c>
+      <c r="E60" s="3">
         <v>6810300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7094300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7364100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7133400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5720100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5779400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7512400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7709200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7759900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7777400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6834000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6523800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6108100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6746200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6521400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7681200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9642900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9884400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10103900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10132600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9978100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10562900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7275400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6971300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5228200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5569100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4645000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4560300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4157600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4587800</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11772200</v>
+      </c>
+      <c r="E61" s="3">
         <v>12580700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12658700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12659000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12973600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14354600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14218200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14491500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14923100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16228700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16353500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>17237400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>17412900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18242600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18015200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18724500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19206400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18762500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19717100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>19854300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20917000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>22102200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>22429200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9101500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8994400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11197800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11214300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12460500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>12590100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>13086900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>13161200</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1449800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1482700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1410900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1172200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1165400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1193600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1292000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1190400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1116300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1173800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>847200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>966100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>976900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1004500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4188500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4234400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4432100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4613800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4748600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4970900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5727600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5484200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5606800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2318300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2443500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2457200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2588300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2484600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2763700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2770500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2818800</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20784200</v>
+      </c>
+      <c r="E66" s="3">
         <v>22176900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22481800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22702800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22841000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22824500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22865400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24961700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25810000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27329400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27218100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27877000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27851900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28362300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28949900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29480300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31319700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33019200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34350100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34929100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>36777200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>37564500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>38598900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18695200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18409200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18883200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19371700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19590100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19914100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20015000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20567800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-330700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-211900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-388300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-48200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>80000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>227900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3418800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4082000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4133900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4607500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4639700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5553000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5369100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5252500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5175600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4312500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4106800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3941500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3688800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4087000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3909900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4323600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5361200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6277000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6091500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6051900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6031100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6010600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5820800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5989300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6010700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14260400</v>
+      </c>
+      <c r="E76" s="3">
         <v>14657700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14711300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15217600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15570500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15650400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18635500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19792400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19520000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20014300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20467400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20865600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20843300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20927900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21072300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19182300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19805400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20447700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20492700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21141300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21206900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21414700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22954100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12547900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11746200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11262700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11883800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11463400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11902800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11891600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12167100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E81" s="3">
         <v>176400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-340100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-128200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3042000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-516500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>94800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-326400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>113900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-765600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>331600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>264000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>224700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1011200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>354300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>313900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>399200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-263800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>311500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-279200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1037600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-915800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>185700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>39400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>20800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>20500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>189800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-168500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>51200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7202,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E83" s="3">
         <v>93500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>561600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>95000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>189100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>90000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>44500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>95400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>95500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>126700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>89800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>83600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>88200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>87900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>869800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>699500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>722300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>736000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>749800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1017100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1317100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1422500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>953100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>432300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>415700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>415000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>547700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>469700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>501400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>500500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>608900</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>381800</v>
+      </c>
+      <c r="E89" s="3">
         <v>388300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>815800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>744900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>219700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>535500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>482700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>826500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>379100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>614600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>568500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>835200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>525100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>971200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>142600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>869000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>802500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1138500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>523100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1085600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>559400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>848800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>36200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>525000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>379500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>291100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>686700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>487800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>668900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-39700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>636100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7924,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-39900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-196500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-86800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-42600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-140400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-77000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-49800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-165500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-95900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-67800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-165900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-115700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-89500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-71900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-221400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-131900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-89300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-116900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-44500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-43400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-73600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-44100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-53100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-114700</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-51600</v>
+      </c>
+      <c r="E94" s="3">
         <v>277400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-211200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-98900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-52500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-65100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-168700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1747900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>375800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-154300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>26700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-86800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-749500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1784500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-115000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-82100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-66900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-219100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-118200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-16800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>236300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-58700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-74500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-145600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-114500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-176900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-158400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-75600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-175600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,52 +8352,53 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>139800</v>
+      </c>
+      <c r="E96" s="3">
         <v>139600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>138200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>139900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>139800</v>
-      </c>
-      <c r="H96" s="3">
-        <v>143300</v>
       </c>
       <c r="I96" s="3">
         <v>143300</v>
       </c>
       <c r="J96" s="3">
+        <v>143300</v>
+      </c>
+      <c r="K96" s="3">
         <v>143200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>145500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>142800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>144000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>143900</v>
       </c>
       <c r="O96" s="3">
         <v>143900</v>
       </c>
       <c r="P96" s="3">
+        <v>143900</v>
+      </c>
+      <c r="Q96" s="3">
         <v>143800</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-145500</v>
       </c>
       <c r="R96" s="3">
         <v>-145500</v>
@@ -8173,16 +8407,16 @@
         <v>-145500</v>
       </c>
       <c r="T96" s="3">
+        <v>-145500</v>
+      </c>
+      <c r="U96" s="3">
         <v>-145100</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-133000</v>
       </c>
       <c r="V96" s="3">
         <v>-133000</v>
       </c>
       <c r="W96" s="3">
-        <v>0</v>
+        <v>-133000</v>
       </c>
       <c r="X96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8742,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1242600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-203800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-236400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-228100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-362400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-467000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1420200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1636700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-847900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-425600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-926100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-97600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-303500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-974700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1330600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-758700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-779600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1009000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-349200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-877500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-685500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1099800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>149100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-145700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-584300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-464400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-132700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-531800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-40100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-576200</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E101" s="3">
         <v>16800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-37800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>23900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-14100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>15600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-28800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>15600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-14300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-28800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-11400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-10300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-7300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-22200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>19800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>21800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>16100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-23900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-16500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-915700</v>
+      </c>
+      <c r="E102" s="3">
         <v>457700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>344500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>435700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-188500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1144000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>961600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-97400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>22300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-318200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>680400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>120700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-751800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>612100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-88000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>51200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-55500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>82600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-134000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-36900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>182800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>342400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-263200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>96800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>116700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>161700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-158400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-113800</v>
       </c>
     </row>
